--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8131,6 +8131,130 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>114681354</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57248</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kronoparken, Lagmanskvarn, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>583844</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6346664</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8255,6 +8255,121 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>114938940</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kronoparken, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>583794</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6346547</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Gunnar Westling</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Gunnar Westling</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8257,10 +8257,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>114938940</v>
+        <v>114681356</v>
       </c>
       <c r="B65" t="n">
-        <v>97538</v>
+        <v>57597</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8269,53 +8269,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kronoparken, Sm</t>
+          <t>Kronoparken, Lagmanskvarn, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>583794</v>
+        <v>583844</v>
       </c>
       <c r="R65" t="n">
-        <v>6346547</v>
+        <v>6346664</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8339,12 +8339,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8353,22 +8363,136 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>114938940</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97538</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kronoparken, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>583794</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6346547</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
           <t>Gunnar Westling</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>Gunnar Westling</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -9486,10 +9486,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118609265</v>
+        <v>118609158</v>
       </c>
       <c r="B76" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9498,25 +9498,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583747</v>
+        <v>583816</v>
       </c>
       <c r="R76" t="n">
-        <v>6346513</v>
+        <v>6346476</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9556,12 +9556,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9581,17 +9581,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118609158</v>
+        <v>118609265</v>
       </c>
       <c r="B77" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9600,25 +9600,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583816</v>
+        <v>583747</v>
       </c>
       <c r="R77" t="n">
-        <v>6346476</v>
+        <v>6346513</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -9486,10 +9486,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118609158</v>
+        <v>118609084</v>
       </c>
       <c r="B76" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9498,25 +9498,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583816</v>
+        <v>583798</v>
       </c>
       <c r="R76" t="n">
-        <v>6346476</v>
+        <v>6346511</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9556,12 +9556,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9588,10 +9588,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118609265</v>
+        <v>118609072</v>
       </c>
       <c r="B77" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9600,25 +9600,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583747</v>
+        <v>583759</v>
       </c>
       <c r="R77" t="n">
-        <v>6346513</v>
+        <v>6346583</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118609182</v>
+        <v>118609158</v>
       </c>
       <c r="B78" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9702,25 +9702,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583784</v>
+        <v>583816</v>
       </c>
       <c r="R78" t="n">
-        <v>6346474</v>
+        <v>6346476</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9785,17 +9785,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118609196</v>
+        <v>118609266</v>
       </c>
       <c r="B79" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9804,25 +9804,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583690</v>
+        <v>583777</v>
       </c>
       <c r="R79" t="n">
-        <v>6346703</v>
+        <v>6346452</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118609268</v>
+        <v>118609265</v>
       </c>
       <c r="B81" t="n">
         <v>97846</v>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583785</v>
+        <v>583747</v>
       </c>
       <c r="R81" t="n">
-        <v>6346532</v>
+        <v>6346513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10098,7 +10098,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118609195</v>
+        <v>118609194</v>
       </c>
       <c r="B82" t="n">
         <v>90524</v>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583823</v>
+        <v>583776</v>
       </c>
       <c r="R82" t="n">
-        <v>6346477</v>
+        <v>6346453</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10200,10 +10200,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118609266</v>
+        <v>118609087</v>
       </c>
       <c r="B83" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583777</v>
+        <v>583736</v>
       </c>
       <c r="R83" t="n">
-        <v>6346452</v>
+        <v>6346536</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10295,14 +10295,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118609309</v>
+        <v>118609182</v>
       </c>
       <c r="B84" t="n">
         <v>90524</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583823</v>
+        <v>583784</v>
       </c>
       <c r="R84" t="n">
-        <v>6346454</v>
+        <v>6346474</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10397,14 +10397,14 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ida Johansson</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118609084</v>
+        <v>118609092</v>
       </c>
       <c r="B85" t="n">
         <v>90524</v>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583798</v>
+        <v>583528</v>
       </c>
       <c r="R85" t="n">
-        <v>6346511</v>
+        <v>6346552</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10506,7 +10506,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118609092</v>
+        <v>118609309</v>
       </c>
       <c r="B86" t="n">
         <v>90524</v>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583528</v>
+        <v>583823</v>
       </c>
       <c r="R86" t="n">
-        <v>6346552</v>
+        <v>6346454</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10601,14 +10601,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ida Johansson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118609244</v>
+        <v>118609268</v>
       </c>
       <c r="B87" t="n">
         <v>97846</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583749</v>
+        <v>583785</v>
       </c>
       <c r="R87" t="n">
-        <v>6346506</v>
+        <v>6346532</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10678,12 +10678,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10710,7 +10710,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118609269</v>
+        <v>118609244</v>
       </c>
       <c r="B88" t="n">
         <v>97846</v>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>583798</v>
+        <v>583749</v>
       </c>
       <c r="R88" t="n">
-        <v>6346492</v>
+        <v>6346506</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10812,7 +10812,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118609194</v>
+        <v>118609332</v>
       </c>
       <c r="B89" t="n">
         <v>90524</v>
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583776</v>
+        <v>583825</v>
       </c>
       <c r="R89" t="n">
-        <v>6346453</v>
+        <v>6346473</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10882,12 +10882,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10907,14 +10907,14 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth, Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118609087</v>
+        <v>118609195</v>
       </c>
       <c r="B90" t="n">
         <v>90524</v>
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583736</v>
+        <v>583823</v>
       </c>
       <c r="R90" t="n">
-        <v>6346536</v>
+        <v>6346477</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11009,14 +11009,14 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118609332</v>
+        <v>118609196</v>
       </c>
       <c r="B91" t="n">
         <v>90524</v>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583825</v>
+        <v>583690</v>
       </c>
       <c r="R91" t="n">
-        <v>6346473</v>
+        <v>6346703</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11086,12 +11086,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Andreas Lundqvist</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11220,10 +11220,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118609072</v>
+        <v>118609269</v>
       </c>
       <c r="B93" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11232,25 +11232,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583759</v>
+        <v>583798</v>
       </c>
       <c r="R93" t="n">
-        <v>6346583</v>
+        <v>6346492</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11290,12 +11290,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -9486,7 +9486,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118609084</v>
+        <v>118609195</v>
       </c>
       <c r="B76" t="n">
         <v>90524</v>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583798</v>
+        <v>583823</v>
       </c>
       <c r="R76" t="n">
-        <v>6346511</v>
+        <v>6346477</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9581,14 +9581,14 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118609072</v>
+        <v>118609194</v>
       </c>
       <c r="B77" t="n">
         <v>90524</v>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583759</v>
+        <v>583776</v>
       </c>
       <c r="R77" t="n">
-        <v>6346583</v>
+        <v>6346453</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118609158</v>
+        <v>118609084</v>
       </c>
       <c r="B78" t="n">
-        <v>94620</v>
+        <v>90524</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9702,25 +9702,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583816</v>
+        <v>583798</v>
       </c>
       <c r="R78" t="n">
-        <v>6346476</v>
+        <v>6346511</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9887,14 +9887,14 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118609085</v>
+        <v>118609332</v>
       </c>
       <c r="B80" t="n">
         <v>90524</v>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583783</v>
+        <v>583825</v>
       </c>
       <c r="R80" t="n">
-        <v>6346470</v>
+        <v>6346473</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118609265</v>
+        <v>118609196</v>
       </c>
       <c r="B81" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10008,25 +10008,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583747</v>
+        <v>583690</v>
       </c>
       <c r="R81" t="n">
-        <v>6346513</v>
+        <v>6346703</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10098,10 +10098,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118609194</v>
+        <v>118609157</v>
       </c>
       <c r="B82" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10110,25 +10110,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583776</v>
+        <v>583794</v>
       </c>
       <c r="R82" t="n">
-        <v>6346453</v>
+        <v>6346411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10193,14 +10193,14 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118609087</v>
+        <v>118609092</v>
       </c>
       <c r="B83" t="n">
         <v>90524</v>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583736</v>
+        <v>583528</v>
       </c>
       <c r="R83" t="n">
-        <v>6346536</v>
+        <v>6346552</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10302,10 +10302,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118609182</v>
+        <v>118609244</v>
       </c>
       <c r="B84" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10314,25 +10314,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583784</v>
+        <v>583749</v>
       </c>
       <c r="R84" t="n">
-        <v>6346474</v>
+        <v>6346506</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10372,12 +10372,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10397,17 +10397,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118609092</v>
+        <v>118609269</v>
       </c>
       <c r="B85" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10416,25 +10416,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583528</v>
+        <v>583798</v>
       </c>
       <c r="R85" t="n">
-        <v>6346552</v>
+        <v>6346492</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10499,14 +10499,14 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118609309</v>
+        <v>118609072</v>
       </c>
       <c r="B86" t="n">
         <v>90524</v>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583823</v>
+        <v>583759</v>
       </c>
       <c r="R86" t="n">
-        <v>6346454</v>
+        <v>6346583</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10601,17 +10601,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ida Johansson</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118609268</v>
+        <v>118609182</v>
       </c>
       <c r="B87" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10620,25 +10620,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583785</v>
+        <v>583784</v>
       </c>
       <c r="R87" t="n">
-        <v>6346532</v>
+        <v>6346474</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10710,10 +10710,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118609244</v>
+        <v>118609087</v>
       </c>
       <c r="B88" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10722,25 +10722,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>583749</v>
+        <v>583736</v>
       </c>
       <c r="R88" t="n">
-        <v>6346506</v>
+        <v>6346536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10805,14 +10805,14 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118609332</v>
+        <v>118609085</v>
       </c>
       <c r="B89" t="n">
         <v>90524</v>
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583825</v>
+        <v>583783</v>
       </c>
       <c r="R89" t="n">
-        <v>6346473</v>
+        <v>6346470</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10882,12 +10882,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Andreas Lundqvist</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118609195</v>
+        <v>118609158</v>
       </c>
       <c r="B90" t="n">
-        <v>90524</v>
+        <v>94620</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10926,25 +10926,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583823</v>
+        <v>583816</v>
       </c>
       <c r="R90" t="n">
-        <v>6346477</v>
+        <v>6346476</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11009,17 +11009,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118609196</v>
+        <v>118609268</v>
       </c>
       <c r="B91" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11028,25 +11028,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583690</v>
+        <v>583785</v>
       </c>
       <c r="R91" t="n">
-        <v>6346703</v>
+        <v>6346532</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11086,12 +11086,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11111,17 +11111,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118609157</v>
+        <v>118609265</v>
       </c>
       <c r="B92" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11130,25 +11130,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583794</v>
+        <v>583747</v>
       </c>
       <c r="R92" t="n">
-        <v>6346411</v>
+        <v>6346513</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11213,17 +11213,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118609269</v>
+        <v>118609309</v>
       </c>
       <c r="B93" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11232,25 +11232,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583798</v>
+        <v>583823</v>
       </c>
       <c r="R93" t="n">
-        <v>6346492</v>
+        <v>6346454</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth, Ida Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -9486,10 +9486,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118609195</v>
+        <v>118609265</v>
       </c>
       <c r="B76" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9498,25 +9498,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583823</v>
+        <v>583747</v>
       </c>
       <c r="R76" t="n">
-        <v>6346477</v>
+        <v>6346513</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9588,10 +9588,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118609194</v>
+        <v>118609158</v>
       </c>
       <c r="B77" t="n">
-        <v>90524</v>
+        <v>94627</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9600,25 +9600,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583776</v>
+        <v>583816</v>
       </c>
       <c r="R77" t="n">
-        <v>6346453</v>
+        <v>6346476</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118609084</v>
+        <v>118609157</v>
       </c>
       <c r="B78" t="n">
-        <v>90524</v>
+        <v>94627</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9702,25 +9702,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583798</v>
+        <v>583794</v>
       </c>
       <c r="R78" t="n">
-        <v>6346511</v>
+        <v>6346411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9795,7 +9795,7 @@
         <v>118609266</v>
       </c>
       <c r="B79" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9887,17 +9887,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118609332</v>
+        <v>118609244</v>
       </c>
       <c r="B80" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9906,25 +9906,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583825</v>
+        <v>583749</v>
       </c>
       <c r="R80" t="n">
-        <v>6346473</v>
+        <v>6346506</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Andreas Lundqvist</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118609196</v>
+        <v>118609309</v>
       </c>
       <c r="B81" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583690</v>
+        <v>583823</v>
       </c>
       <c r="R81" t="n">
-        <v>6346703</v>
+        <v>6346454</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth, Ida Johansson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118609157</v>
+        <v>118609092</v>
       </c>
       <c r="B82" t="n">
-        <v>94620</v>
+        <v>90531</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10110,25 +10110,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>583794</v>
+        <v>583528</v>
       </c>
       <c r="R82" t="n">
-        <v>6346411</v>
+        <v>6346552</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10200,10 +10200,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118609092</v>
+        <v>118609196</v>
       </c>
       <c r="B83" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583528</v>
+        <v>583690</v>
       </c>
       <c r="R83" t="n">
-        <v>6346552</v>
+        <v>6346703</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10295,17 +10295,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118609244</v>
+        <v>118609194</v>
       </c>
       <c r="B84" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10314,25 +10314,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583749</v>
+        <v>583776</v>
       </c>
       <c r="R84" t="n">
-        <v>6346506</v>
+        <v>6346453</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10372,12 +10372,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10397,17 +10397,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118609269</v>
+        <v>118609085</v>
       </c>
       <c r="B85" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10416,25 +10416,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583798</v>
+        <v>583783</v>
       </c>
       <c r="R85" t="n">
-        <v>6346492</v>
+        <v>6346470</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10499,17 +10499,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118609072</v>
+        <v>118609269</v>
       </c>
       <c r="B86" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10518,25 +10518,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583759</v>
+        <v>583798</v>
       </c>
       <c r="R86" t="n">
-        <v>6346583</v>
+        <v>6346492</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10601,17 +10601,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118609182</v>
+        <v>118609072</v>
       </c>
       <c r="B87" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583784</v>
+        <v>583759</v>
       </c>
       <c r="R87" t="n">
-        <v>6346474</v>
+        <v>6346583</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10678,12 +10678,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10703,17 +10703,17 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118609087</v>
+        <v>118609268</v>
       </c>
       <c r="B88" t="n">
-        <v>90524</v>
+        <v>97853</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10722,25 +10722,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>583736</v>
+        <v>583785</v>
       </c>
       <c r="R88" t="n">
-        <v>6346536</v>
+        <v>6346532</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118609085</v>
+        <v>118609084</v>
       </c>
       <c r="B89" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583783</v>
+        <v>583798</v>
       </c>
       <c r="R89" t="n">
-        <v>6346470</v>
+        <v>6346511</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10914,10 +10914,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118609158</v>
+        <v>118609195</v>
       </c>
       <c r="B90" t="n">
-        <v>94620</v>
+        <v>90531</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10926,25 +10926,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583816</v>
+        <v>583823</v>
       </c>
       <c r="R90" t="n">
-        <v>6346476</v>
+        <v>6346477</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11009,17 +11009,17 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118609268</v>
+        <v>118609087</v>
       </c>
       <c r="B91" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11028,25 +11028,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583785</v>
+        <v>583736</v>
       </c>
       <c r="R91" t="n">
-        <v>6346532</v>
+        <v>6346536</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11086,12 +11086,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11111,17 +11111,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118609265</v>
+        <v>118609182</v>
       </c>
       <c r="B92" t="n">
-        <v>97846</v>
+        <v>90531</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11130,25 +11130,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583747</v>
+        <v>583784</v>
       </c>
       <c r="R92" t="n">
-        <v>6346513</v>
+        <v>6346474</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11213,17 +11213,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118609309</v>
+        <v>118609332</v>
       </c>
       <c r="B93" t="n">
-        <v>90524</v>
+        <v>90531</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583823</v>
+        <v>583825</v>
       </c>
       <c r="R93" t="n">
-        <v>6346454</v>
+        <v>6346473</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ida Johansson</t>
+          <t>Louise Lindroth, Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -9486,10 +9486,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118609265</v>
+        <v>118609072</v>
       </c>
       <c r="B76" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9498,25 +9498,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>583747</v>
+        <v>583759</v>
       </c>
       <c r="R76" t="n">
-        <v>6346513</v>
+        <v>6346583</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9556,12 +9556,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9581,17 +9581,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118609158</v>
+        <v>118609268</v>
       </c>
       <c r="B77" t="n">
-        <v>94627</v>
+        <v>97853</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9600,25 +9600,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>583816</v>
+        <v>583785</v>
       </c>
       <c r="R77" t="n">
-        <v>6346476</v>
+        <v>6346532</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118609157</v>
+        <v>118609085</v>
       </c>
       <c r="B78" t="n">
-        <v>94627</v>
+        <v>90531</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9702,25 +9702,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9730,10 +9730,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>583794</v>
+        <v>583783</v>
       </c>
       <c r="R78" t="n">
-        <v>6346411</v>
+        <v>6346470</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9792,10 +9792,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118609266</v>
+        <v>118609196</v>
       </c>
       <c r="B79" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9804,25 +9804,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>583777</v>
+        <v>583690</v>
       </c>
       <c r="R79" t="n">
-        <v>6346452</v>
+        <v>6346703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9894,10 +9894,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118609244</v>
+        <v>118609195</v>
       </c>
       <c r="B80" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9906,25 +9906,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>583749</v>
+        <v>583823</v>
       </c>
       <c r="R80" t="n">
-        <v>6346506</v>
+        <v>6346477</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9996,10 +9996,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118609309</v>
+        <v>118609266</v>
       </c>
       <c r="B81" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10008,25 +10008,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>583823</v>
+        <v>583777</v>
       </c>
       <c r="R81" t="n">
-        <v>6346454</v>
+        <v>6346452</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10066,12 +10066,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ida Johansson</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -10200,10 +10200,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118609196</v>
+        <v>118609269</v>
       </c>
       <c r="B83" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10212,25 +10212,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10240,10 +10240,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>583690</v>
+        <v>583798</v>
       </c>
       <c r="R83" t="n">
-        <v>6346703</v>
+        <v>6346492</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10302,10 +10302,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118609194</v>
+        <v>118609265</v>
       </c>
       <c r="B84" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10314,25 +10314,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>583776</v>
+        <v>583747</v>
       </c>
       <c r="R84" t="n">
-        <v>6346453</v>
+        <v>6346513</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118609085</v>
+        <v>118609244</v>
       </c>
       <c r="B85" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10416,25 +10416,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>583783</v>
+        <v>583749</v>
       </c>
       <c r="R85" t="n">
-        <v>6346470</v>
+        <v>6346506</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10474,12 +10474,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10499,17 +10499,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118609269</v>
+        <v>118609332</v>
       </c>
       <c r="B86" t="n">
-        <v>97853</v>
+        <v>90531</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10518,25 +10518,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10546,10 +10546,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>583798</v>
+        <v>583825</v>
       </c>
       <c r="R86" t="n">
-        <v>6346492</v>
+        <v>6346473</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10601,14 +10601,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth, Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118609072</v>
+        <v>118609084</v>
       </c>
       <c r="B87" t="n">
         <v>90531</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>583759</v>
+        <v>583798</v>
       </c>
       <c r="R87" t="n">
-        <v>6346583</v>
+        <v>6346511</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10678,12 +10678,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10710,10 +10710,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118609268</v>
+        <v>118609157</v>
       </c>
       <c r="B88" t="n">
-        <v>97853</v>
+        <v>94627</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10722,25 +10722,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10750,10 +10750,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>583785</v>
+        <v>583794</v>
       </c>
       <c r="R88" t="n">
-        <v>6346532</v>
+        <v>6346411</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118609084</v>
+        <v>118609158</v>
       </c>
       <c r="B89" t="n">
-        <v>90531</v>
+        <v>94627</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10824,25 +10824,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10852,10 +10852,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>583798</v>
+        <v>583816</v>
       </c>
       <c r="R89" t="n">
-        <v>6346511</v>
+        <v>6346476</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10882,12 +10882,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10914,7 +10914,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118609195</v>
+        <v>118609087</v>
       </c>
       <c r="B90" t="n">
         <v>90531</v>
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>583823</v>
+        <v>583736</v>
       </c>
       <c r="R90" t="n">
-        <v>6346477</v>
+        <v>6346536</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11009,14 +11009,14 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Louise Lindroth</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118609087</v>
+        <v>118609182</v>
       </c>
       <c r="B91" t="n">
         <v>90531</v>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>583736</v>
+        <v>583784</v>
       </c>
       <c r="R91" t="n">
-        <v>6346536</v>
+        <v>6346474</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11086,12 +11086,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11111,14 +11111,14 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Louise Lindroth</t>
+          <t>Louise Lindroth, Ieva Mardega</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118609182</v>
+        <v>118609194</v>
       </c>
       <c r="B92" t="n">
         <v>90531</v>
@@ -11158,10 +11158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>583784</v>
+        <v>583776</v>
       </c>
       <c r="R92" t="n">
-        <v>6346474</v>
+        <v>6346453</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11220,7 +11220,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118609332</v>
+        <v>118609309</v>
       </c>
       <c r="B93" t="n">
         <v>90531</v>
@@ -11260,10 +11260,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>583825</v>
+        <v>583823</v>
       </c>
       <c r="R93" t="n">
-        <v>6346473</v>
+        <v>6346454</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Andreas Lundqvist</t>
+          <t>Louise Lindroth, Ida Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11320,6 +11320,231 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121495315</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57720</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Kronoparken, Sneshorvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>583685</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6346519</v>
+      </c>
+      <c r="S94" t="n">
+        <v>25</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121495310</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98095</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Kronoparken, Sneshorvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>583685</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6346519</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11322,10 +11322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121495315</v>
+        <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>98095</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11334,39 +11334,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11418,6 +11414,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11436,10 +11433,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121495310</v>
+        <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>98095</v>
+        <v>57720</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11448,35 +11445,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11528,7 +11529,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11325,7 +11325,7 @@
         <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11436,7 +11436,7 @@
         <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11325,7 +11325,7 @@
         <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>57724</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11325,7 +11325,7 @@
         <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11436,7 +11436,7 @@
         <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Anneli Brenander, Jan Brenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11322,10 +11322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121495310</v>
+        <v>121495315</v>
       </c>
       <c r="B94" t="n">
-        <v>98105</v>
+        <v>57725</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11334,35 +11334,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11414,7 +11418,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11426,17 +11429,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121495315</v>
+        <v>121495310</v>
       </c>
       <c r="B95" t="n">
-        <v>57725</v>
+        <v>98105</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11445,39 +11448,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11529,6 +11528,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11322,10 +11322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121495315</v>
+        <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>57725</v>
+        <v>98105</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11334,39 +11334,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11418,6 +11414,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11436,10 +11433,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121495310</v>
+        <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>98105</v>
+        <v>57725</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11448,35 +11445,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11528,7 +11529,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11322,10 +11322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121495310</v>
+        <v>121495315</v>
       </c>
       <c r="B94" t="n">
-        <v>98105</v>
+        <v>57725</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11334,35 +11334,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11414,7 +11418,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11433,10 +11436,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121495315</v>
+        <v>121495310</v>
       </c>
       <c r="B95" t="n">
-        <v>57725</v>
+        <v>98105</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11445,39 +11448,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11529,6 +11528,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11429,7 +11429,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -11322,10 +11322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121495315</v>
+        <v>121495310</v>
       </c>
       <c r="B94" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11334,39 +11334,35 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11418,6 +11414,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -11436,10 +11433,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121495310</v>
+        <v>121495315</v>
       </c>
       <c r="B95" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11448,35 +11445,39 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11528,7 +11529,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -8601,7 +8601,7 @@
         <v>118157713</v>
       </c>
       <c r="B68" t="n">
-        <v>57296</v>
+        <v>57484</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -8601,7 +8601,7 @@
         <v>118157713</v>
       </c>
       <c r="B68" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -8601,7 +8601,7 @@
         <v>118157713</v>
       </c>
       <c r="B68" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Louise Lindroth, Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -8601,7 +8601,7 @@
         <v>118157713</v>
       </c>
       <c r="B68" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 5747-2020 artfynd.xlsx
+++ b/artfynd/A 5747-2020 artfynd.xlsx
@@ -8601,7 +8601,7 @@
         <v>118157713</v>
       </c>
       <c r="B68" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
